--- a/artfynd/A 24204-2024 artfynd.xlsx
+++ b/artfynd/A 24204-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>26155150</v>
+        <v>95938296</v>
       </c>
       <c r="B2" t="n">
-        <v>56314</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102110</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455360.7958586465</v>
+        <v>455361</v>
       </c>
       <c r="R2" t="n">
-        <v>6927327.732458812</v>
+        <v>6927328</v>
       </c>
       <c r="S2" t="n">
         <v>78</v>
@@ -754,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-05-20</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-05-20</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I tallskogen vid trapporna.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,44 +787,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Svensson</t>
+          <t>Andreas Viberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Svensson</t>
+          <t>Andreas Viberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>26579955</v>
+        <v>110785649</v>
       </c>
       <c r="B3" t="n">
-        <v>55902</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102961</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,34 +829,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455360.7958586465</v>
+        <v>455361</v>
       </c>
       <c r="R3" t="n">
-        <v>6927327.732458812</v>
+        <v>6927328</v>
       </c>
       <c r="S3" t="n">
         <v>78</v>
@@ -885,27 +872,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 km nedströms om angiven lokal</t>
+          <t>1 hona, 2 juv, stöttes på stigen mellan väg 315 och fallet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,49 +907,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heurlin</t>
+          <t>Anders Fredriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heurlin</t>
+          <t>Anders Fredriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60220255</v>
+        <v>26155150</v>
       </c>
       <c r="B4" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>102110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -970,11 +952,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455360.7958586465</v>
+        <v>455361</v>
       </c>
       <c r="R4" t="n">
-        <v>6927327.732458812</v>
+        <v>6927328</v>
       </c>
       <c r="S4" t="n">
         <v>78</v>
@@ -1013,17 +993,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-15</t>
+          <t>2007-05-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-15</t>
+          <t>2007-05-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1043,27 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Apelgren</t>
+          <t>Thomas Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Apelgren</t>
+          <t>Thomas Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95938296</v>
+        <v>26579955</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,46 +1046,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102961</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455360.7958586465</v>
+        <v>455361</v>
       </c>
       <c r="R5" t="n">
-        <v>6927327.732458812</v>
+        <v>6927328</v>
       </c>
       <c r="S5" t="n">
         <v>78</v>
@@ -1137,27 +1119,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I tallskogen vid trapporna.</t>
+          <t>1 km nedströms om angiven lokal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,61 +1154,59 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Viberg</t>
+          <t>Anders Heurlin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Viberg</t>
+          <t>Anders Heurlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114875371</v>
+        <v>100370531</v>
       </c>
       <c r="B6" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
@@ -1263,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,15 +1273,589 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Mats Axbrink</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Axbrink, Cecilia Krohn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>60220255</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>455361</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6927328</v>
+      </c>
+      <c r="S7" t="n">
+        <v>78</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Apelgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Apelgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114875371</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>455361</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6927328</v>
+      </c>
+      <c r="S8" t="n">
+        <v>78</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Karin Oknemark</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Karin Oknemark</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>46538291</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>455361</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6927328</v>
+      </c>
+      <c r="S9" t="n">
+        <v>78</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-06-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-06-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maths Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maths Nilsson, Camilla Nyqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>60230092</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sångbäcksfallet, Röjan, Klövsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>455361</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6927328</v>
+      </c>
+      <c r="S10" t="n">
+        <v>78</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-06-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-06-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Apelgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Apelgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100868264</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sångbäcksfallet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>455366</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6927304</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1937-08-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1937-08-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Modin</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Thorvald Langes Jämtlands kärlväxtflora 1937 plus några till</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24204-2024 artfynd.xlsx
+++ b/artfynd/A 24204-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95938296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110785649</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26155150</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26579955</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100370531</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60220255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114875371</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1632,6 +1672,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/46538291</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1750,6 +1795,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60230092</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1856,8 +1906,25 @@
           <t>Thorvald Langes Jämtlands kärlväxtflora 1937 plus några till</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100868264</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>